--- a/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>112 ROSA RICHTER DE AYARZA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.937959</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-74.250469</v>
-      </c>
-      <c r="I2" t="n">
-        <v>366</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.937959</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-74.250469</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>38254 LUIS CAVERO BENDEZU / LUIS CAVERO BENDEZU</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.93606</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-74.24379999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>590</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.93606</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-74.2438</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>GONZALEZ VIGIL</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.94297</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-74.24575</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2627</v>
-      </c>
-      <c r="J4" t="n">
-        <v>161</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.94297</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-74.24575</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>38256 MARIA URRIBARRI GOMEZ / MARIA URRIBARRI GOMEZ</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.94082</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-74.24579</v>
-      </c>
-      <c r="I5" t="n">
-        <v>393</v>
-      </c>
-      <c r="J5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.94082</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-74.24579</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>38257 SAN RAMON</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.937574</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-74.252528</v>
-      </c>
-      <c r="I6" t="n">
-        <v>871</v>
-      </c>
-      <c r="J6" t="n">
-        <v>39</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.937574</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-74.252528</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.93441</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-74.24181</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="J7" t="n">
-        <v>106</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.93441</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-74.24181</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>38266 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.938195</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-74.252161</v>
-      </c>
-      <c r="I8" t="n">
-        <v>828</v>
-      </c>
-      <c r="J8" t="n">
-        <v>34</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.938195</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-74.252161</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>38267 SAN FRANCISCO DE ASIS / SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.9354</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-74.24850000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1732</v>
-      </c>
-      <c r="J9" t="n">
-        <v>82</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.9354</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-74.2485</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>39013 CLARA CASTILLO DE GAYOZZO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.941262</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.248665</v>
-      </c>
-      <c r="I10" t="n">
-        <v>285</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.941262</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.248665</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>ESMERALDA DE LOS ANDES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.94327</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-74.25524</v>
-      </c>
-      <c r="I11" t="n">
-        <v>512</v>
-      </c>
-      <c r="J11" t="n">
-        <v>33</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.94327</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-74.25524</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.94181</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-74.24703</v>
-      </c>
-      <c r="I12" t="n">
-        <v>448</v>
-      </c>
-      <c r="J12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.94181</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-74.24703</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>LUTHER KING SCHOOL</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.94321</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-74.24538</v>
-      </c>
-      <c r="I13" t="n">
-        <v>167</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.94321</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-74.24538</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>SAN ALFONSO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.94291</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-74.24459</v>
-      </c>
-      <c r="I14" t="n">
-        <v>499</v>
-      </c>
-      <c r="J14" t="n">
-        <v>26</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.94291</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-74.24459</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>HUANTA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.92415</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-74.26299</v>
-      </c>
-      <c r="I15" t="n">
-        <v>328</v>
-      </c>
-      <c r="J15" t="n">
-        <v>34</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.92415</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-74.26299</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.9231</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-74.26101</v>
-      </c>
-      <c r="I16" t="n">
-        <v>424</v>
-      </c>
-      <c r="J16" t="n">
-        <v>25</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.9231</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-74.26101</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>79395</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>112 ROSA RICHTER DE AYARZA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.937959</t>
+          <t>-12.93441</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.250469</t>
+          <t>-74.24181</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79357</t>
+          <t>559385</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38254 LUIS CAVERO BENDEZU / LUIS CAVERO BENDEZU</t>
+          <t>LUTHER KING SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.93606</t>
+          <t>-12.94321</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.2438</t>
+          <t>-74.24538</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>167</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79362</t>
+          <t>79300</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GONZALEZ VIGIL</t>
+          <t>112 ROSA RICHTER DE AYARZA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.94297</t>
+          <t>-12.937959</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.24575</t>
+          <t>-74.250469</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79376</t>
+          <t>79908</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38256 MARIA URRIBARRI GOMEZ / MARIA URRIBARRI GOMEZ</t>
+          <t>39013 CLARA CASTILLO DE GAYOZZO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.94082</t>
+          <t>-12.941262</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.24579</t>
+          <t>-74.248665</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79381</t>
+          <t>79362</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38257 SAN RAMON</t>
+          <t>GONZALEZ VIGIL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.937574</t>
+          <t>-12.94297</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.252528</t>
+          <t>-74.24575</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79395</t>
+          <t>607517</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.93441</t>
+          <t>-12.9231</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.24181</t>
+          <t>-74.26101</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79456</t>
+          <t>79376</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38266 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>38256 MARIA URRIBARRI GOMEZ / MARIA URRIBARRI GOMEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.938195</t>
+          <t>-12.94082</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.252161</t>
+          <t>-74.24579</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>559366</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38267 SAN FRANCISCO DE ASIS / SAN FRANCISCO DE ASIS</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.9354</t>
+          <t>-12.94181</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.2485</t>
+          <t>-74.24703</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79908</t>
+          <t>561500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39013 CLARA CASTILLO DE GAYOZZO</t>
+          <t>SAN ALFONSO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.941262</t>
+          <t>-12.94291</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.248665</t>
+          <t>-74.24459</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>499</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>559366</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>38266 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.94181</t>
+          <t>-12.938195</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.24703</t>
+          <t>-74.252161</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>828</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>559385</t>
+          <t>562217</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LUTHER KING SCHOOL</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.94321</t>
+          <t>-12.92415</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.24538</t>
+          <t>-74.26299</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>561500</t>
+          <t>79357</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN ALFONSO</t>
+          <t>38254 LUIS CAVERO BENDEZU / LUIS CAVERO BENDEZU</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.94291</t>
+          <t>-12.93606</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.24459</t>
+          <t>-74.2438</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>590</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>562217</t>
+          <t>79381</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>38257 SAN RAMON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.92415</t>
+          <t>-12.937574</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.26299</t>
+          <t>-74.252528</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>607517</t>
+          <t>79461</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>38267 SAN FRANCISCO DE ASIS / SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.9231</t>
+          <t>-12.9354</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.26101</t>
+          <t>-74.2485</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">

--- a/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79395</t>
+          <t>607517</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.93441</t>
+          <t>424</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.24181</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>-12.9231</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-74.26101</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>559385</t>
+          <t>562217</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LUTHER KING SCHOOL</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.94321</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.24538</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>-12.92415</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.26299</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>561500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>112 ROSA RICHTER DE AYARZA</t>
+          <t>SAN ALFONSO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.937959</t>
+          <t>499</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.250469</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-12.94291</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.24459</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79908</t>
+          <t>559385</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39013 CLARA CASTILLO DE GAYOZZO</t>
+          <t>LUTHER KING SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.941262</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.248665</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.94321</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-74.24538</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79362</t>
+          <t>559366</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GONZALEZ VIGIL</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.94297</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.24575</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>-12.94181</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>-74.24703</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>607517</t>
+          <t>079951</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>ESMERALDA DE LOS ANDES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.9231</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.26101</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>-12.94327</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-74.25524</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79376</t>
+          <t>079908</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38256 MARIA URRIBARRI GOMEZ / MARIA URRIBARRI GOMEZ</t>
+          <t>39013 CLARA CASTILLO DE GAYOZZO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.94082</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.24579</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-12.941262</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-74.248665</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>559366</t>
+          <t>079461</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>38267 SAN FRANCISCO DE ASIS / SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.94181</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.24703</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-12.9354</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-74.2485</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>561500</t>
+          <t>079456</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAN ALFONSO</t>
+          <t>38266 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.94291</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.24459</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>-12.938195</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-74.252161</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79951</t>
+          <t>079395</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ESMERALDA DE LOS ANDES</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.94327</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.25524</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>-12.93441</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-74.24181</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79456</t>
+          <t>079381</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38266 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>38257 SAN RAMON</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.938195</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.252161</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>-12.937574</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-74.252528</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>562217</t>
+          <t>079376</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>38256 MARIA URRIBARRI GOMEZ / MARIA URRIBARRI GOMEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.92415</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.26299</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-12.94082</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-74.24579</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79357</t>
+          <t>079362</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38254 LUIS CAVERO BENDEZU / LUIS CAVERO BENDEZU</t>
+          <t>GONZALEZ VIGIL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.93606</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.2438</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>-12.94297</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.24575</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79381</t>
+          <t>079357</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38257 SAN RAMON</t>
+          <t>38254 LUIS CAVERO BENDEZU / LUIS CAVERO BENDEZU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.937574</t>
+          <t>590</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.252528</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>-12.93606</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-74.2438</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>079300</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38267 SAN FRANCISCO DE ASIS / SAN FRANCISCO DE ASIS</t>
+          <t>112 ROSA RICHTER DE AYARZA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.9354</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.2485</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>-12.937959</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-74.250469</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">

--- a/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/ZonasEscolares/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
